--- a/02_DIA_inicio_2026_analisis_assets/rbd_9734_escuela-raul-saez-saez_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9734_escuela-raul-saez-saez_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA6CCD26-1212-4EEE-99BB-E7E14308DF72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79CA5A69-0C2E-4B17-B6ED-D3CCDB471AB7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF15EE4-7BED-449D-BFD0-65AEEBA285C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF52C903-E9A2-419C-8CB8-AF2AA2FF8230}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{973437D9-ECD9-4AA8-8C24-2F129860402C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31DDF531-FD0C-42AB-A924-45D3C6AE5F87}"/>
 </file>